--- a/wxdgaming.game.basic/src/main/cfg/活动.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/活动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="25110" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="q_activity" sheetId="4" r:id="rId1"/>
@@ -160,13 +160,13 @@
     <t>OpenDay|gte|1;OpenDay|lte|999</t>
   </si>
   <si>
-    <t>{"cron":"0 0 8 ? * ? ?","timeUnit":"MINUTES","duration":800,"openDay":5, "hefuDay":5}</t>
+    <t>{"cron":"0 0 8 * * ?","timeUnit":"MINUTES","duration":800,"openDay":5, "hefuDay":5}</t>
   </si>
   <si>
     <t>活动2</t>
   </si>
   <si>
-    <t>{"cron":"0 0 8 ? * ? ?","timeUnit":"MINUTES","duration":800}</t>
+    <t>{"cron":"0 0 8 * * ?","timeUnit":"MINUTES","duration":800}</t>
   </si>
   <si>
     <t>活动3</t>
@@ -1177,7 +1177,7 @@
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/wxdgaming.game.basic/src/main/cfg/活动.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/活动.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25110" windowHeight="9720"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="q_activity" sheetId="4" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>活动</t>
   </si>
@@ -121,6 +121,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>poll</t>
+  </si>
+  <si>
     <t>validation</t>
   </si>
   <si>
@@ -136,9 +139,6 @@
     <t>wxdgaming.boot2.core.lang.ConfigString</t>
   </si>
   <si>
-    <t>wxdgaming.boot2.core.timer.CronExpress</t>
-  </si>
-  <si>
     <t>活动流水号</t>
   </si>
   <si>
@@ -148,6 +148,9 @@
     <t>名称</t>
   </si>
   <si>
+    <t>是否循环</t>
+  </si>
+  <si>
     <t>限制条件</t>
   </si>
   <si>
@@ -160,13 +163,13 @@
     <t>OpenDay|gte|1;OpenDay|lte|999</t>
   </si>
   <si>
-    <t>{"cron":"0 0 8 * * ?","timeUnit":"MINUTES","duration":800,"openDay":5, "hefuDay":5}</t>
+    <t>CurrentDayMin#0&amp;CurrentDayMax#0</t>
   </si>
   <si>
     <t>活动2</t>
   </si>
   <si>
-    <t>{"cron":"0 0 8 * * ?","timeUnit":"MINUTES","duration":800}</t>
+    <t>HHmmss#200000&amp;minute#30</t>
   </si>
   <si>
     <t>活动3</t>
@@ -1162,22 +1165,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.3833333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="76" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="2"/>
-    <col min="9" max="9" width="48.375" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="17.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.3833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="76" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="48.375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1188,8 +1191,9 @@
       <c r="F1"/>
       <c r="G1"/>
       <c r="H1"/>
+      <c r="I1"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1202,15 +1206,18 @@
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1226,33 +1233,39 @@
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1268,12 +1281,15 @@
       <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>1001</v>
       </c>
@@ -1281,147 +1297,168 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
         <v>17</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6"/>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
       <c r="G6"/>
       <c r="H6"/>
       <c r="I6"/>
+      <c r="J6"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>1002</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7"/>
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7"/>
+      <c r="J7"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>1003</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8"/>
       <c r="G8"/>
       <c r="H8"/>
       <c r="I8"/>
+      <c r="J8"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>1004</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9"/>
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
       <c r="G9"/>
       <c r="H9"/>
       <c r="I9"/>
+      <c r="J9"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>1005</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10"/>
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10"/>
+      <c r="J10"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>1006</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11"/>
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
       <c r="G11"/>
       <c r="H11"/>
       <c r="I11"/>
+      <c r="J11"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>1007</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12"/>
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
+      <c r="J12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C13:D1048576">
+  <conditionalFormatting sqref="C13:E1048576">
     <cfRule type="containsText" dxfId="0" priority="29" operator="between" text="102133005">
       <formula>NOT(ISERROR(SEARCH("102133005",C13)))</formula>
     </cfRule>

--- a/wxdgaming.game.basic/src/main/cfg/活动.xlsx
+++ b/wxdgaming.game.basic/src/main/cfg/活动.xlsx
@@ -160,7 +160,7 @@
     <t>活动1</t>
   </si>
   <si>
-    <t>OpenDay|gte|1;OpenDay|lte|999</t>
+    <t>OpenDay#&gt;=#1&amp;OpenDay#&lt;=#999</t>
   </si>
   <si>
     <t>CurrentDayMin#0&amp;CurrentDayMax#0</t>
@@ -1171,7 +1171,7 @@
     <col min="1" max="1" width="11.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.5" style="1" customWidth="1"/>
     <col min="3" max="4" width="17.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.3833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="30.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="76" style="1" customWidth="1"/>
     <col min="7" max="7" width="32.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="32.5" style="1" customWidth="1"/>
